--- a/results.xlsx
+++ b/results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="63">
   <si>
     <t>Timestamp</t>
   </si>
@@ -163,21 +163,12 @@
     <t xml:space="preserve">PDV data should be post-processed to report velocity-time history, spall strength, and HEL values by using these hyper-parameters and the characterization function from Piyush. </t>
   </si>
   <si>
-    <t>pdv_results/C1--20250807--00001-velocity-v1_3_1-PBU.csv</t>
-  </si>
-  <si>
-    <t>pdv_results/C1--20250807--00003-velocity-v1_3_1-Q4Y.csv</t>
-  </si>
-  <si>
     <t>Flyer position for each experiment should be recorded. Additionally, the %composition or the gradation pattern should be recorded.</t>
   </si>
   <si>
     <t>Laser target energy should be post-processed to report the Flyer impact velocity by using the calibration curves from Piyush.</t>
   </si>
   <si>
-    <t>pdv_results/C1--20250807--00002-velocity-v1_3_1-DMX.csv</t>
-  </si>
-  <si>
     <t>Beam--20250807--00001</t>
   </si>
   <si>
@@ -197,6 +188,21 @@
   </si>
   <si>
     <t>Sucessful laser shot</t>
+  </si>
+  <si>
+    <t>pdv_results/C1--20250807--00001-velocity-v1_3_1-FAV.csv</t>
+  </si>
+  <si>
+    <t>pdv_results/C1--20250807--00002-velocity-v1_3_1-N90.csv</t>
+  </si>
+  <si>
+    <t>pdv_results/C1--20250807--00003-velocity-v1_3_1-HCF.csv</t>
+  </si>
+  <si>
+    <t>pdv_results/C1--20250807--00004-velocity-v1_3_1-PEA.csv</t>
+  </si>
+  <si>
+    <t>pdv_results/C1--20250807--00004-velocity-v1_3_1-ZY8.csv</t>
   </si>
 </sst>
 </file>
@@ -558,10 +564,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH7"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:37">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -664,8 +670,17 @@
       <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="AI1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:37">
       <c r="A2" s="2">
         <v>45876.76770663194</v>
       </c>
@@ -714,12 +729,6 @@
       <c r="Q2">
         <v>-9.44</v>
       </c>
-      <c r="R2" t="s">
-        <v>49</v>
-      </c>
-      <c r="S2" t="s">
-        <v>50</v>
-      </c>
       <c r="U2">
         <v>1</v>
       </c>
@@ -744,20 +753,26 @@
       <c r="AC2">
         <v>752.15</v>
       </c>
-      <c r="AD2" t="s">
-        <v>53</v>
-      </c>
       <c r="AE2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="AG2">
         <v>6.57</v>
       </c>
       <c r="AH2" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AJ2">
+        <v>1.603643006678255</v>
+      </c>
+      <c r="AK2">
+        <v>99217696.45903906</v>
       </c>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:37">
       <c r="A3" s="2">
         <v>45876.76780840278</v>
       </c>
@@ -806,12 +821,6 @@
       <c r="Q3">
         <v>-7.23</v>
       </c>
-      <c r="R3">
-        <v>1.603643006678255</v>
-      </c>
-      <c r="S3">
-        <v>3.711136780709246</v>
-      </c>
       <c r="U3">
         <v>2</v>
       </c>
@@ -836,20 +845,26 @@
       <c r="AC3">
         <v>752.15</v>
       </c>
-      <c r="AD3">
-        <v>3.097376450418284</v>
-      </c>
       <c r="AE3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="AG3">
         <v>7.42</v>
       </c>
       <c r="AH3" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ3">
+        <v>3.097376450418284</v>
+      </c>
+      <c r="AK3">
+        <v>118334812.9160956</v>
       </c>
     </row>
-    <row r="4" spans="1:34">
+    <row r="4" spans="1:37">
       <c r="A4" s="2">
         <v>45876.76791054398</v>
       </c>
@@ -898,12 +913,6 @@
       <c r="Q4">
         <v>-3.72</v>
       </c>
-      <c r="R4">
-        <v>99217696.45903906</v>
-      </c>
-      <c r="S4">
-        <v>72818800.35847729</v>
-      </c>
       <c r="U4">
         <v>3</v>
       </c>
@@ -928,20 +937,26 @@
       <c r="AC4">
         <v>752.15</v>
       </c>
-      <c r="AD4">
-        <v>118334812.9160956</v>
-      </c>
       <c r="AE4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AG4">
         <v>7.53</v>
       </c>
       <c r="AH4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AI4" t="s">
         <v>60</v>
       </c>
+      <c r="AJ4">
+        <v>3.711136780709246</v>
+      </c>
+      <c r="AK4">
+        <v>72818800.35847729</v>
+      </c>
     </row>
-    <row r="5" spans="1:34">
+    <row r="5" spans="1:37">
       <c r="A5" s="2">
         <v>45876.76800179398</v>
       </c>
@@ -1015,16 +1030,25 @@
         <v>750.59</v>
       </c>
       <c r="AE5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="AG5">
         <v>6.6</v>
       </c>
       <c r="AH5" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ5">
+        <v>3.762069578482503</v>
+      </c>
+      <c r="AK5">
+        <v>82435216.46354869</v>
       </c>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:37">
       <c r="A6" s="2">
         <v>45876.76800179398</v>
       </c>
@@ -1098,16 +1122,25 @@
         <v>750.59</v>
       </c>
       <c r="AE6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="AG6">
         <v>6.6</v>
       </c>
       <c r="AH6" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ6">
+        <v>3.762069578482503</v>
+      </c>
+      <c r="AK6">
+        <v>82435216.46354869</v>
       </c>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:37">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -1124,16 +1157,16 @@
         <v>48</v>
       </c>
       <c r="U7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AC7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AE7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="AG7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
